--- a/task_submission/3.1 性能自验证报告.xlsx
+++ b/task_submission/3.1 性能自验证报告.xlsx
@@ -760,6 +760,38 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="11430000" cy="7143750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="06a3884e-ddea-42bf-9f2f-6e002c58d914"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R00747ab14a94493c"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -1005,14 +1037,16 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" customHeight="1">
-      <x:c r="A1" s="13" t="str">
-        <x:v>性能测试总结：开发环境自测，任务书同机基线比值尚未验证
-1、Ascend910_9382 / CANN 9.1.0；指定 OS/驱动待复测。
-2、计划 35，适用 10，官方绝对耗时门槛通过 10，失败 0；其余 25 不适用。
-3、同机基线 10 项未测；E/G 列不可计算，C 列标记“待补基线”。
-4、预热 50 次，每轮 200 次，共 5 轮；F 为轮均值中位数，含分配/提交/完成，单位 us。
-5、shape=[B,H,L,D]；完整形状、阈值及全部样本见“完整统计”；截图待补。
-6、rato 按模板为 F/E（当前/标杆，越小越好）；绝对阈值不能当作基线。</x:v>
+      <x:c r="A1" s="13" t="inlineStr">
+        <x:is>
+          <x:t>性能补测：同机基线与提交实现，2026-10-29，批次02
+1、Ascend910_9382 / CANN9.1.0；指定OS/driver仍待复测。
+2、10个基线及提交实现逐位精度均通过；候选views_concat_q_copy。
+3、50预热/200次×5轮；E为基线、F为提交中位数(us)，G=F/E。
+4、随包绝对门限：通过5，超限5；原件及两批数据完整保留。
+5、任务书比值上限列量纲歧义仍待确认；不将参考耗时当作基线。
+6、真实VS Code终端截图位于D40；35个ID完整保留。</x:t>
+        </x:is>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -1091,21 +1125,25 @@
       <x:c r="B5" s="17" t="str">
         <x:v>float16</x:v>
       </x:c>
-      <x:c r="C5" s="17" t="str">
-        <x:v>待补基线</x:v>
-      </x:c>
-      <x:c r="D5" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
-      </x:c>
-      <x:c r="E5" t="str" s="19">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="F5" s="20" t="n">
-        <x:f>'完整统计'!X3</x:f>
-        <x:v>18.595299999999998</x:v>
-      </x:c>
-      <x:c r="G5" t="str" s="19">
-        <x:v>不可计算</x:v>
+      <x:c r="C5" s="17" t="inlineStr">
+        <x:is>
+          <x:t>不通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="19">
+        <x:v>104.90285</x:v>
+      </x:c>
+      <x:c r="F5" s="20">
+        <x:v>29.16815</x:v>
+      </x:c>
+      <x:c r="G5" s="19">
+        <x:f>F5/E5</x:f>
+        <x:v>0.27804916644304706</x:v>
       </x:c>
       <x:c r="H5" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_001_float16_random</x:v>
@@ -1196,21 +1234,25 @@
       <x:c r="B9" s="17" t="str">
         <x:v>float16</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str">
-        <x:v>待补基线</x:v>
-      </x:c>
-      <x:c r="D9" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
-      </x:c>
-      <x:c r="E9" t="str" s="19">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="F9" s="20" t="n">
-        <x:f>'完整统计'!X7</x:f>
-        <x:v>18.30965</x:v>
-      </x:c>
-      <x:c r="G9" t="str" s="19">
-        <x:v>不可计算</x:v>
+      <x:c r="C9" s="17" t="inlineStr">
+        <x:is>
+          <x:t>不通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="19">
+        <x:v>124.92205</x:v>
+      </x:c>
+      <x:c r="F9" s="20">
+        <x:v>28.5098</x:v>
+      </x:c>
+      <x:c r="G9" s="19">
+        <x:f>F9/E9</x:f>
+        <x:v>0.22822071844001918</x:v>
       </x:c>
       <x:c r="H9" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_005_float16_random</x:v>
@@ -1223,21 +1265,25 @@
       <x:c r="B10" s="17" t="str">
         <x:v>float16</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str">
-        <x:v>待补基线</x:v>
-      </x:c>
-      <x:c r="D10" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
-      </x:c>
-      <x:c r="E10" t="str" s="19">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="F10" s="20" t="n">
-        <x:f>'完整统计'!X8</x:f>
-        <x:v>19.0145</x:v>
-      </x:c>
-      <x:c r="G10" t="str" s="19">
-        <x:v>不可计算</x:v>
+      <x:c r="C10" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="19">
+        <x:v>97.94575</x:v>
+      </x:c>
+      <x:c r="F10" s="20">
+        <x:v>17.2037</x:v>
+      </x:c>
+      <x:c r="G10" s="19">
+        <x:f>F10/E10</x:f>
+        <x:v>0.17564519134316703</x:v>
       </x:c>
       <x:c r="H10" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_006_float16_random</x:v>
@@ -1250,21 +1296,25 @@
       <x:c r="B11" s="17" t="str">
         <x:v>float16</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str">
-        <x:v>待补基线</x:v>
-      </x:c>
-      <x:c r="D11" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
-      </x:c>
-      <x:c r="E11" t="str" s="19">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="F11" s="20" t="n">
-        <x:f>'完整统计'!X9</x:f>
-        <x:v>74.29594999999999</x:v>
-      </x:c>
-      <x:c r="G11" t="str" s="19">
-        <x:v>不可计算</x:v>
+      <x:c r="C11" s="17" t="inlineStr">
+        <x:is>
+          <x:t>不通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="19">
+        <x:v>212.4332</x:v>
+      </x:c>
+      <x:c r="F11" s="20">
+        <x:v>76.63885</x:v>
+      </x:c>
+      <x:c r="G11" s="19">
+        <x:f>F11/E11</x:f>
+        <x:v>0.3607668198756127</x:v>
       </x:c>
       <x:c r="H11" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_007_float16_random</x:v>
@@ -1277,21 +1327,25 @@
       <x:c r="B12" s="17" t="str">
         <x:v>float16</x:v>
       </x:c>
-      <x:c r="C12" s="17" t="str">
-        <x:v>待补基线</x:v>
-      </x:c>
-      <x:c r="D12" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
-      </x:c>
-      <x:c r="E12" t="str" s="19">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="F12" s="20" t="n">
-        <x:f>'完整统计'!X10</x:f>
-        <x:v>18.6017</x:v>
-      </x:c>
-      <x:c r="G12" t="str" s="19">
-        <x:v>不可计算</x:v>
+      <x:c r="C12" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="19">
+        <x:v>103.08539999999999</x:v>
+      </x:c>
+      <x:c r="F12" s="20">
+        <x:v>17.421650000000003</x:v>
+      </x:c>
+      <x:c r="G12" s="19">
+        <x:f>F12/E12</x:f>
+        <x:v>0.16900210893104167</x:v>
       </x:c>
       <x:c r="H12" s="18" t="str">
         <x:v>T5SplitQkvAppendCache_008_float16_random</x:v>
@@ -1356,21 +1410,25 @@
       <x:c r="B15" s="17" t="str">
         <x:v>bfloat16</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="str">
-        <x:v>待补基线</x:v>
-      </x:c>
-      <x:c r="D15" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
-      </x:c>
-      <x:c r="E15" t="str" s="15">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="F15" s="21" t="n">
-        <x:f>'完整统计'!X13</x:f>
-        <x:v>17.7452</x:v>
-      </x:c>
-      <x:c r="G15" t="str" s="15">
-        <x:v>不可计算</x:v>
+      <x:c r="C15" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="15">
+        <x:v>93.73725</x:v>
+      </x:c>
+      <x:c r="F15" s="21">
+        <x:v>17.80325</x:v>
+      </x:c>
+      <x:c r="G15" s="15">
+        <x:f>F15/E15</x:f>
+        <x:v>0.18992716342755947</x:v>
       </x:c>
       <x:c r="H15" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_011_bfloat16_random</x:v>
@@ -1461,21 +1519,25 @@
       <x:c r="B19" s="17" t="str">
         <x:v>bfloat16</x:v>
       </x:c>
-      <x:c r="C19" s="17" t="str">
-        <x:v>待补基线</x:v>
-      </x:c>
-      <x:c r="D19" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
-      </x:c>
-      <x:c r="E19" t="str" s="15">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="F19" s="21" t="n">
-        <x:f>'完整统计'!X17</x:f>
-        <x:v>18.149849999999997</x:v>
-      </x:c>
-      <x:c r="G19" t="str" s="15">
-        <x:v>不可计算</x:v>
+      <x:c r="C19" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" s="15">
+        <x:v>100.106</x:v>
+      </x:c>
+      <x:c r="F19" s="21">
+        <x:v>17.51285</x:v>
+      </x:c>
+      <x:c r="G19" s="15">
+        <x:f>F19/E19</x:f>
+        <x:v>0.17494306035602264</x:v>
       </x:c>
       <x:c r="H19" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_015_bfloat16_random</x:v>
@@ -1488,21 +1550,25 @@
       <x:c r="B20" s="17" t="str">
         <x:v>bfloat16</x:v>
       </x:c>
-      <x:c r="C20" s="17" t="str">
-        <x:v>待补基线</x:v>
-      </x:c>
-      <x:c r="D20" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
-      </x:c>
-      <x:c r="E20" t="str" s="15">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="F20" s="21" t="n">
-        <x:f>'完整统计'!X18</x:f>
-        <x:v>18.63915</x:v>
-      </x:c>
-      <x:c r="G20" t="str" s="15">
-        <x:v>不可计算</x:v>
+      <x:c r="C20" s="17" t="inlineStr">
+        <x:is>
+          <x:t>通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" s="15">
+        <x:v>104.2181</x:v>
+      </x:c>
+      <x:c r="F20" s="21">
+        <x:v>19.2744</x:v>
+      </x:c>
+      <x:c r="G20" s="15">
+        <x:f>F20/E20</x:f>
+        <x:v>0.18494292258254563</x:v>
       </x:c>
       <x:c r="H20" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_016_bfloat16_random</x:v>
@@ -1515,21 +1581,25 @@
       <x:c r="B21" s="17" t="str">
         <x:v>bfloat16</x:v>
       </x:c>
-      <x:c r="C21" s="17" t="str">
-        <x:v>待补基线</x:v>
-      </x:c>
-      <x:c r="D21" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
-      </x:c>
-      <x:c r="E21" t="str" s="15">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="F21" s="21" t="n">
-        <x:f>'完整统计'!X19</x:f>
-        <x:v>75.40325</x:v>
-      </x:c>
-      <x:c r="G21" t="str" s="15">
-        <x:v>不可计算</x:v>
+      <x:c r="C21" s="17" t="inlineStr">
+        <x:is>
+          <x:t>不通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="15">
+        <x:v>213.8891</x:v>
+      </x:c>
+      <x:c r="F21" s="21">
+        <x:v>81.7386</x:v>
+      </x:c>
+      <x:c r="G21" s="15">
+        <x:f>F21/E21</x:f>
+        <x:v>0.3821541163154177</x:v>
       </x:c>
       <x:c r="H21" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_017_bfloat16_random</x:v>
@@ -1542,21 +1612,25 @@
       <x:c r="B22" s="17" t="str">
         <x:v>bfloat16</x:v>
       </x:c>
-      <x:c r="C22" s="17" t="str">
-        <x:v>待补基线</x:v>
-      </x:c>
-      <x:c r="D22" t="str" s="15">
-        <x:v>缺现场截图；原始日志见本包</x:v>
-      </x:c>
-      <x:c r="E22" t="str" s="15">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="F22" s="21" t="n">
-        <x:f>'完整统计'!X20</x:f>
-        <x:v>18.9619</x:v>
-      </x:c>
-      <x:c r="G22" t="str" s="15">
-        <x:v>不可计算</x:v>
+      <x:c r="C22" s="17" t="inlineStr">
+        <x:is>
+          <x:t>不通过</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="15" t="inlineStr">
+        <x:is>
+          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" s="15">
+        <x:v>113.4895</x:v>
+      </x:c>
+      <x:c r="F22" s="21">
+        <x:v>31.4493</x:v>
+      </x:c>
+      <x:c r="G22" s="15">
+        <x:f>F22/E22</x:f>
+        <x:v>0.2771119795223347</x:v>
       </x:c>
       <x:c r="H22" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_018_bfloat16_random</x:v>
@@ -2028,6 +2102,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6718b40127f4e97"/>
 </x:worksheet>
 </file>
 
@@ -2321,58 +2396,60 @@
       <x:c r="P3" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q3" s="7" t="str">
-        <x:v>绝对门槛通过；基线待测</x:v>
+      <x:c r="Q3" s="7" t="inlineStr">
+        <x:is>
+          <x:t>绝对门限超限；同机基线已测</x:t>
+        </x:is>
       </x:c>
       <x:c r="R3" s="11" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="S3" s="11" t="n">
-        <x:v>21.562</x:v>
-      </x:c>
-      <x:c r="T3" s="11" t="n">
-        <x:v>18.4133</x:v>
-      </x:c>
-      <x:c r="U3" s="11" t="n">
-        <x:v>18.02705</x:v>
-      </x:c>
-      <x:c r="V3" s="11" t="n">
-        <x:v>18.595299999999998</x:v>
-      </x:c>
-      <x:c r="W3" s="11" t="n">
-        <x:v>18.59845</x:v>
-      </x:c>
-      <x:c r="X3" s="11" t="n">
-        <x:f>MEDIAN(S3:W3)</x:f>
-        <x:v>18.595299999999998</x:v>
-      </x:c>
-      <x:c r="Y3" s="11" t="n">
-        <x:v>16.98199987411499</x:v>
-      </x:c>
-      <x:c r="Z3" s="11" t="n">
-        <x:v>17.927299737930298</x:v>
-      </x:c>
-      <x:c r="AA3" s="11" t="n">
-        <x:v>17.572200298309326</x:v>
-      </x:c>
-      <x:c r="AB3" s="11" t="n">
-        <x:v>18.088500499725342</x:v>
-      </x:c>
-      <x:c r="AC3" s="11" t="n">
-        <x:v>17.972899675369263</x:v>
-      </x:c>
-      <x:c r="AD3" s="11" t="n">
-        <x:f>MEDIAN(Y3:AC3)</x:f>
-        <x:v>17.927299737930298</x:v>
-      </x:c>
-      <x:c r="AE3" s="7" t="str">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="AF3" s="7" t="str">
-        <x:v>不可计算</x:v>
-      </x:c>
-      <x:c r="AG3" s="7" t="str">
-        <x:v>raw/reports/final_176_01/performance.json#/cases/0</x:v>
+      <x:c r="S3" s="11">
+        <x:v>32.1837</x:v>
+      </x:c>
+      <x:c r="T3" s="11">
+        <x:v>29.398400000000002</x:v>
+      </x:c>
+      <x:c r="U3" s="11">
+        <x:v>28.626150000000003</x:v>
+      </x:c>
+      <x:c r="V3" s="11">
+        <x:v>29.16815</x:v>
+      </x:c>
+      <x:c r="W3" s="11">
+        <x:v>27.9892</x:v>
+      </x:c>
+      <x:c r="X3" s="11">
+        <x:v>29.16815</x:v>
+      </x:c>
+      <x:c r="Y3" s="11">
+        <x:v>24.71060037612915</x:v>
+      </x:c>
+      <x:c r="Z3" s="11">
+        <x:v>28.576500415802002</x:v>
+      </x:c>
+      <x:c r="AA3" s="11">
+        <x:v>27.731099128723145</x:v>
+      </x:c>
+      <x:c r="AB3" s="11">
+        <x:v>28.26390027999878</x:v>
+      </x:c>
+      <x:c r="AC3" s="11">
+        <x:v>27.02310085296631</x:v>
+      </x:c>
+      <x:c r="AD3" s="11">
+        <x:v>27.731099128723145</x:v>
+      </x:c>
+      <x:c r="AE3" s="7">
+        <x:v>104.90285</x:v>
+      </x:c>
+      <x:c r="AF3" s="7">
+        <x:v>0.27804916644304706</x:v>
+      </x:c>
+      <x:c r="AG3" s="7" t="inlineStr">
+        <x:is>
+          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -2727,58 +2804,60 @@
       <x:c r="P7" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q7" s="7" t="str">
-        <x:v>绝对门槛通过；基线待测</x:v>
+      <x:c r="Q7" s="7" t="inlineStr">
+        <x:is>
+          <x:t>绝对门限超限；同机基线已测</x:t>
+        </x:is>
       </x:c>
       <x:c r="R7" s="11" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="S7" s="11" t="n">
-        <x:v>18.08835</x:v>
-      </x:c>
-      <x:c r="T7" s="11" t="n">
-        <x:v>18.169400000000003</x:v>
-      </x:c>
-      <x:c r="U7" s="11" t="n">
-        <x:v>18.30965</x:v>
-      </x:c>
-      <x:c r="V7" s="11" t="n">
-        <x:v>18.948349999999998</x:v>
-      </x:c>
-      <x:c r="W7" s="11" t="n">
-        <x:v>18.5559</x:v>
-      </x:c>
-      <x:c r="X7" s="11" t="n">
-        <x:f>MEDIAN(S7:W7)</x:f>
-        <x:v>18.30965</x:v>
-      </x:c>
-      <x:c r="Y7" s="11" t="n">
-        <x:v>17.404600381851196</x:v>
-      </x:c>
-      <x:c r="Z7" s="11" t="n">
-        <x:v>17.55470037460327</x:v>
-      </x:c>
-      <x:c r="AA7" s="11" t="n">
-        <x:v>17.707500457763672</x:v>
-      </x:c>
-      <x:c r="AB7" s="11" t="n">
-        <x:v>17.781800031661987</x:v>
-      </x:c>
-      <x:c r="AC7" s="11" t="n">
-        <x:v>18.10520052909851</x:v>
-      </x:c>
-      <x:c r="AD7" s="11" t="n">
-        <x:f>MEDIAN(Y7:AC7)</x:f>
-        <x:v>17.707500457763672</x:v>
-      </x:c>
-      <x:c r="AE7" s="7" t="str">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="AF7" s="7" t="str">
-        <x:v>不可计算</x:v>
-      </x:c>
-      <x:c r="AG7" s="7" t="str">
-        <x:v>raw/reports/final_176_01/performance.json#/cases/1</x:v>
+      <x:c r="S7" s="11">
+        <x:v>32.4208</x:v>
+      </x:c>
+      <x:c r="T7" s="11">
+        <x:v>30.59</x:v>
+      </x:c>
+      <x:c r="U7" s="11">
+        <x:v>28.5098</x:v>
+      </x:c>
+      <x:c r="V7" s="11">
+        <x:v>27.13</x:v>
+      </x:c>
+      <x:c r="W7" s="11">
+        <x:v>26.8835</x:v>
+      </x:c>
+      <x:c r="X7" s="11">
+        <x:v>28.5098</x:v>
+      </x:c>
+      <x:c r="Y7" s="11">
+        <x:v>29.621200561523438</x:v>
+      </x:c>
+      <x:c r="Z7" s="11">
+        <x:v>29.86870050430298</x:v>
+      </x:c>
+      <x:c r="AA7" s="11">
+        <x:v>27.83479928970337</x:v>
+      </x:c>
+      <x:c r="AB7" s="11">
+        <x:v>26.314499378204346</x:v>
+      </x:c>
+      <x:c r="AC7" s="11">
+        <x:v>26.095199584960938</x:v>
+      </x:c>
+      <x:c r="AD7" s="11">
+        <x:v>27.83479928970337</x:v>
+      </x:c>
+      <x:c r="AE7" s="7">
+        <x:v>124.92205</x:v>
+      </x:c>
+      <x:c r="AF7" s="7">
+        <x:v>0.22822071844001918</x:v>
+      </x:c>
+      <x:c r="AG7" s="7" t="inlineStr">
+        <x:is>
+          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -2830,58 +2909,60 @@
       <x:c r="P8" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q8" s="7" t="str">
-        <x:v>绝对门槛通过；基线待测</x:v>
+      <x:c r="Q8" s="7" t="inlineStr">
+        <x:is>
+          <x:t>绝对门限通过；同机基线已测</x:t>
+        </x:is>
       </x:c>
       <x:c r="R8" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="S8" s="11" t="n">
-        <x:v>19.8518</x:v>
-      </x:c>
-      <x:c r="T8" s="11" t="n">
-        <x:v>18.675549999999998</x:v>
-      </x:c>
-      <x:c r="U8" s="11" t="n">
-        <x:v>18.841150000000003</x:v>
-      </x:c>
-      <x:c r="V8" s="11" t="n">
-        <x:v>19.060650000000003</x:v>
-      </x:c>
-      <x:c r="W8" s="11" t="n">
-        <x:v>19.0145</x:v>
-      </x:c>
-      <x:c r="X8" s="11" t="n">
-        <x:f>MEDIAN(S8:W8)</x:f>
-        <x:v>19.0145</x:v>
-      </x:c>
-      <x:c r="Y8" s="11" t="n">
-        <x:v>18.10960054397583</x:v>
-      </x:c>
-      <x:c r="Z8" s="11" t="n">
-        <x:v>18.077800273895264</x:v>
-      </x:c>
-      <x:c r="AA8" s="11" t="n">
-        <x:v>18.06980013847351</x:v>
-      </x:c>
-      <x:c r="AB8" s="11" t="n">
-        <x:v>18.208999633789062</x:v>
-      </x:c>
-      <x:c r="AC8" s="11" t="n">
-        <x:v>18.271299600601196</x:v>
-      </x:c>
-      <x:c r="AD8" s="11" t="n">
-        <x:f>MEDIAN(Y8:AC8)</x:f>
-        <x:v>18.10960054397583</x:v>
-      </x:c>
-      <x:c r="AE8" s="7" t="str">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="AF8" s="7" t="str">
-        <x:v>不可计算</x:v>
-      </x:c>
-      <x:c r="AG8" s="7" t="str">
-        <x:v>raw/reports/final_176_01/performance.json#/cases/2</x:v>
+      <x:c r="S8" s="11">
+        <x:v>16.736849999999997</x:v>
+      </x:c>
+      <x:c r="T8" s="11">
+        <x:v>17.5021</x:v>
+      </x:c>
+      <x:c r="U8" s="11">
+        <x:v>17.3543</x:v>
+      </x:c>
+      <x:c r="V8" s="11">
+        <x:v>16.91</x:v>
+      </x:c>
+      <x:c r="W8" s="11">
+        <x:v>17.2037</x:v>
+      </x:c>
+      <x:c r="X8" s="11">
+        <x:v>17.2037</x:v>
+      </x:c>
+      <x:c r="Y8" s="11">
+        <x:v>15.916099548339844</x:v>
+      </x:c>
+      <x:c r="Z8" s="11">
+        <x:v>16.614500284194946</x:v>
+      </x:c>
+      <x:c r="AA8" s="11">
+        <x:v>16.729700565338135</x:v>
+      </x:c>
+      <x:c r="AB8" s="11">
+        <x:v>16.285799741744995</x:v>
+      </x:c>
+      <x:c r="AC8" s="11">
+        <x:v>16.541999578475952</x:v>
+      </x:c>
+      <x:c r="AD8" s="11">
+        <x:v>16.541999578475952</x:v>
+      </x:c>
+      <x:c r="AE8" s="7">
+        <x:v>97.94575</x:v>
+      </x:c>
+      <x:c r="AF8" s="7">
+        <x:v>0.17564519134316703</x:v>
+      </x:c>
+      <x:c r="AG8" s="7" t="inlineStr">
+        <x:is>
+          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -2933,58 +3014,60 @@
       <x:c r="P9" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q9" s="7" t="str">
-        <x:v>绝对门槛通过；基线待测</x:v>
+      <x:c r="Q9" s="7" t="inlineStr">
+        <x:is>
+          <x:t>绝对门限超限；同机基线已测</x:t>
+        </x:is>
       </x:c>
       <x:c r="R9" s="11" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="S9" s="11" t="n">
-        <x:v>74.25945</x:v>
-      </x:c>
-      <x:c r="T9" s="11" t="n">
-        <x:v>74.61945</x:v>
-      </x:c>
-      <x:c r="U9" s="11" t="n">
-        <x:v>74.78465</x:v>
-      </x:c>
-      <x:c r="V9" s="11" t="n">
-        <x:v>74.27239999999999</x:v>
-      </x:c>
-      <x:c r="W9" s="11" t="n">
-        <x:v>74.29594999999999</x:v>
-      </x:c>
-      <x:c r="X9" s="11" t="n">
-        <x:f>MEDIAN(S9:W9)</x:f>
-        <x:v>74.29594999999999</x:v>
-      </x:c>
-      <x:c r="Y9" s="11" t="n">
-        <x:v>73.58280181884766</x:v>
-      </x:c>
-      <x:c r="Z9" s="11" t="n">
-        <x:v>73.49209785461426</x:v>
-      </x:c>
-      <x:c r="AA9" s="11" t="n">
-        <x:v>73.44900131225586</x:v>
-      </x:c>
-      <x:c r="AB9" s="11" t="n">
-        <x:v>73.43440055847168</x:v>
-      </x:c>
-      <x:c r="AC9" s="11" t="n">
-        <x:v>73.74040126800537</x:v>
-      </x:c>
-      <x:c r="AD9" s="11" t="n">
-        <x:f>MEDIAN(Y9:AC9)</x:f>
-        <x:v>73.49209785461426</x:v>
-      </x:c>
-      <x:c r="AE9" s="7" t="str">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="AF9" s="7" t="str">
-        <x:v>不可计算</x:v>
-      </x:c>
-      <x:c r="AG9" s="7" t="str">
-        <x:v>raw/reports/final_176_01/performance.json#/cases/3</x:v>
+      <x:c r="S9" s="11">
+        <x:v>76.6245</x:v>
+      </x:c>
+      <x:c r="T9" s="11">
+        <x:v>76.63885</x:v>
+      </x:c>
+      <x:c r="U9" s="11">
+        <x:v>76.41855</x:v>
+      </x:c>
+      <x:c r="V9" s="11">
+        <x:v>76.65025</x:v>
+      </x:c>
+      <x:c r="W9" s="11">
+        <x:v>76.6542</x:v>
+      </x:c>
+      <x:c r="X9" s="11">
+        <x:v>76.63885</x:v>
+      </x:c>
+      <x:c r="Y9" s="11">
+        <x:v>75.5472993850708</x:v>
+      </x:c>
+      <x:c r="Z9" s="11">
+        <x:v>75.83179950714111</x:v>
+      </x:c>
+      <x:c r="AA9" s="11">
+        <x:v>75.6633996963501</x:v>
+      </x:c>
+      <x:c r="AB9" s="11">
+        <x:v>75.50049781799316</x:v>
+      </x:c>
+      <x:c r="AC9" s="11">
+        <x:v>75.58720111846924</x:v>
+      </x:c>
+      <x:c r="AD9" s="11">
+        <x:v>75.58720111846924</x:v>
+      </x:c>
+      <x:c r="AE9" s="7">
+        <x:v>212.4332</x:v>
+      </x:c>
+      <x:c r="AF9" s="7">
+        <x:v>0.3607668198756127</x:v>
+      </x:c>
+      <x:c r="AG9" s="7" t="inlineStr">
+        <x:is>
+          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -3036,58 +3119,60 @@
       <x:c r="P10" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q10" s="7" t="str">
-        <x:v>绝对门槛通过；基线待测</x:v>
+      <x:c r="Q10" s="7" t="inlineStr">
+        <x:is>
+          <x:t>绝对门限通过；同机基线已测</x:t>
+        </x:is>
       </x:c>
       <x:c r="R10" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="S10" s="11" t="n">
-        <x:v>18.44215</x:v>
-      </x:c>
-      <x:c r="T10" s="11" t="n">
-        <x:v>18.7622</x:v>
-      </x:c>
-      <x:c r="U10" s="11" t="n">
-        <x:v>18.7393</x:v>
-      </x:c>
-      <x:c r="V10" s="11" t="n">
-        <x:v>18.6017</x:v>
-      </x:c>
-      <x:c r="W10" s="11" t="n">
-        <x:v>18.12875</x:v>
-      </x:c>
-      <x:c r="X10" s="11" t="n">
-        <x:f>MEDIAN(S10:W10)</x:f>
-        <x:v>18.6017</x:v>
-      </x:c>
-      <x:c r="Y10" s="11" t="n">
-        <x:v>17.943300008773804</x:v>
-      </x:c>
-      <x:c r="Z10" s="11" t="n">
-        <x:v>18.266799449920654</x:v>
-      </x:c>
-      <x:c r="AA10" s="11" t="n">
-        <x:v>18.27370047569275</x:v>
-      </x:c>
-      <x:c r="AB10" s="11" t="n">
-        <x:v>18.09749960899353</x:v>
-      </x:c>
-      <x:c r="AC10" s="11" t="n">
-        <x:v>17.727400064468384</x:v>
-      </x:c>
-      <x:c r="AD10" s="11" t="n">
-        <x:f>MEDIAN(Y10:AC10)</x:f>
-        <x:v>18.09749960899353</x:v>
-      </x:c>
-      <x:c r="AE10" s="7" t="str">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="AF10" s="7" t="str">
-        <x:v>不可计算</x:v>
-      </x:c>
-      <x:c r="AG10" s="7" t="str">
-        <x:v>raw/reports/final_176_01/performance.json#/cases/4</x:v>
+      <x:c r="S10" s="11">
+        <x:v>17.62625</x:v>
+      </x:c>
+      <x:c r="T10" s="11">
+        <x:v>17.576400000000003</x:v>
+      </x:c>
+      <x:c r="U10" s="11">
+        <x:v>17.30095</x:v>
+      </x:c>
+      <x:c r="V10" s="11">
+        <x:v>17.421650000000003</x:v>
+      </x:c>
+      <x:c r="W10" s="11">
+        <x:v>17.386400000000002</x:v>
+      </x:c>
+      <x:c r="X10" s="11">
+        <x:v>17.421650000000003</x:v>
+      </x:c>
+      <x:c r="Y10" s="11">
+        <x:v>16.80690050125122</x:v>
+      </x:c>
+      <x:c r="Z10" s="11">
+        <x:v>16.83060050010681</x:v>
+      </x:c>
+      <x:c r="AA10" s="11">
+        <x:v>16.787999868392944</x:v>
+      </x:c>
+      <x:c r="AB10" s="11">
+        <x:v>16.880099773406982</x:v>
+      </x:c>
+      <x:c r="AC10" s="11">
+        <x:v>16.789900064468384</x:v>
+      </x:c>
+      <x:c r="AD10" s="11">
+        <x:v>16.80690050125122</x:v>
+      </x:c>
+      <x:c r="AE10" s="7">
+        <x:v>103.08539999999999</x:v>
+      </x:c>
+      <x:c r="AF10" s="7">
+        <x:v>0.16900210893104167</x:v>
+      </x:c>
+      <x:c r="AG10" s="7" t="inlineStr">
+        <x:is>
+          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -3341,58 +3426,60 @@
       <x:c r="P13" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q13" s="7" t="str">
-        <x:v>绝对门槛通过；基线待测</x:v>
+      <x:c r="Q13" s="7" t="inlineStr">
+        <x:is>
+          <x:t>绝对门限通过；同机基线已测</x:t>
+        </x:is>
       </x:c>
       <x:c r="R13" s="11" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="S13" s="11" t="n">
-        <x:v>17.440849999999998</x:v>
-      </x:c>
-      <x:c r="T13" s="11" t="n">
-        <x:v>18.7892</x:v>
-      </x:c>
-      <x:c r="U13" s="11" t="n">
-        <x:v>18.10455</x:v>
-      </x:c>
-      <x:c r="V13" s="11" t="n">
-        <x:v>17.7452</x:v>
-      </x:c>
-      <x:c r="W13" s="11" t="n">
-        <x:v>17.30635</x:v>
-      </x:c>
-      <x:c r="X13" s="11" t="n">
-        <x:f>MEDIAN(S13:W13)</x:f>
-        <x:v>17.7452</x:v>
-      </x:c>
-      <x:c r="Y13" s="11" t="n">
-        <x:v>16.94980025291443</x:v>
-      </x:c>
-      <x:c r="Z13" s="11" t="n">
-        <x:v>18.312100172042847</x:v>
-      </x:c>
-      <x:c r="AA13" s="11" t="n">
-        <x:v>17.623599767684937</x:v>
-      </x:c>
-      <x:c r="AB13" s="11" t="n">
-        <x:v>17.160500288009644</x:v>
-      </x:c>
-      <x:c r="AC13" s="11" t="n">
-        <x:v>16.791800260543823</x:v>
-      </x:c>
-      <x:c r="AD13" s="11" t="n">
-        <x:f>MEDIAN(Y13:AC13)</x:f>
-        <x:v>17.160500288009644</x:v>
-      </x:c>
-      <x:c r="AE13" s="7" t="str">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="AF13" s="7" t="str">
-        <x:v>不可计算</x:v>
-      </x:c>
-      <x:c r="AG13" s="7" t="str">
-        <x:v>raw/reports/final_176_01/performance.json#/cases/5</x:v>
+      <x:c r="S13" s="11">
+        <x:v>17.8922</x:v>
+      </x:c>
+      <x:c r="T13" s="11">
+        <x:v>19.308799999999998</x:v>
+      </x:c>
+      <x:c r="U13" s="11">
+        <x:v>17.80325</x:v>
+      </x:c>
+      <x:c r="V13" s="11">
+        <x:v>17.04335</x:v>
+      </x:c>
+      <x:c r="W13" s="11">
+        <x:v>16.5578</x:v>
+      </x:c>
+      <x:c r="X13" s="11">
+        <x:v>17.80325</x:v>
+      </x:c>
+      <x:c r="Y13" s="11">
+        <x:v>16.915700435638428</x:v>
+      </x:c>
+      <x:c r="Z13" s="11">
+        <x:v>18.744699954986572</x:v>
+      </x:c>
+      <x:c r="AA13" s="11">
+        <x:v>17.202600240707397</x:v>
+      </x:c>
+      <x:c r="AB13" s="11">
+        <x:v>16.4969003200531</x:v>
+      </x:c>
+      <x:c r="AC13" s="11">
+        <x:v>15.971299409866333</x:v>
+      </x:c>
+      <x:c r="AD13" s="11">
+        <x:v>16.915700435638428</x:v>
+      </x:c>
+      <x:c r="AE13" s="7">
+        <x:v>93.73725</x:v>
+      </x:c>
+      <x:c r="AF13" s="7">
+        <x:v>0.18992716342755947</x:v>
+      </x:c>
+      <x:c r="AG13" s="7" t="inlineStr">
+        <x:is>
+          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
@@ -3747,58 +3834,60 @@
       <x:c r="P17" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q17" s="7" t="str">
-        <x:v>绝对门槛通过；基线待测</x:v>
+      <x:c r="Q17" s="7" t="inlineStr">
+        <x:is>
+          <x:t>绝对门限通过；同机基线已测</x:t>
+        </x:is>
       </x:c>
       <x:c r="R17" s="11" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="S17" s="11" t="n">
-        <x:v>17.807299999999998</x:v>
-      </x:c>
-      <x:c r="T17" s="11" t="n">
-        <x:v>18.455</x:v>
-      </x:c>
-      <x:c r="U17" s="11" t="n">
-        <x:v>18.149849999999997</x:v>
-      </x:c>
-      <x:c r="V17" s="11" t="n">
-        <x:v>18.175099999999997</x:v>
-      </x:c>
-      <x:c r="W17" s="11" t="n">
-        <x:v>17.963849999999997</x:v>
-      </x:c>
-      <x:c r="X17" s="11" t="n">
-        <x:f>MEDIAN(S17:W17)</x:f>
-        <x:v>18.149849999999997</x:v>
-      </x:c>
-      <x:c r="Y17" s="11" t="n">
-        <x:v>17.317999601364136</x:v>
-      </x:c>
-      <x:c r="Z17" s="11" t="n">
-        <x:v>17.980400323867798</x:v>
-      </x:c>
-      <x:c r="AA17" s="11" t="n">
-        <x:v>17.64009952545166</x:v>
-      </x:c>
-      <x:c r="AB17" s="11" t="n">
-        <x:v>17.365200519561768</x:v>
-      </x:c>
-      <x:c r="AC17" s="11" t="n">
-        <x:v>17.550300359725952</x:v>
-      </x:c>
-      <x:c r="AD17" s="11" t="n">
-        <x:f>MEDIAN(Y17:AC17)</x:f>
-        <x:v>17.550300359725952</x:v>
-      </x:c>
-      <x:c r="AE17" s="7" t="str">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="AF17" s="7" t="str">
-        <x:v>不可计算</x:v>
-      </x:c>
-      <x:c r="AG17" s="7" t="str">
-        <x:v>raw/reports/final_176_01/performance.json#/cases/6</x:v>
+      <x:c r="S17" s="11">
+        <x:v>17.2117</x:v>
+      </x:c>
+      <x:c r="T17" s="11">
+        <x:v>17.51285</x:v>
+      </x:c>
+      <x:c r="U17" s="11">
+        <x:v>17.31445</x:v>
+      </x:c>
+      <x:c r="V17" s="11">
+        <x:v>22.8071</x:v>
+      </x:c>
+      <x:c r="W17" s="11">
+        <x:v>25.0058</x:v>
+      </x:c>
+      <x:c r="X17" s="11">
+        <x:v>17.51285</x:v>
+      </x:c>
+      <x:c r="Y17" s="11">
+        <x:v>16.409000158309937</x:v>
+      </x:c>
+      <x:c r="Z17" s="11">
+        <x:v>17.03369975090027</x:v>
+      </x:c>
+      <x:c r="AA17" s="11">
+        <x:v>16.786400079727173</x:v>
+      </x:c>
+      <x:c r="AB17" s="11">
+        <x:v>22.2271990776062</x:v>
+      </x:c>
+      <x:c r="AC17" s="11">
+        <x:v>23.96320104598999</x:v>
+      </x:c>
+      <x:c r="AD17" s="11">
+        <x:v>17.03369975090027</x:v>
+      </x:c>
+      <x:c r="AE17" s="7">
+        <x:v>100.106</x:v>
+      </x:c>
+      <x:c r="AF17" s="7">
+        <x:v>0.17494306035602264</x:v>
+      </x:c>
+      <x:c r="AG17" s="7" t="inlineStr">
+        <x:is>
+          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
@@ -3850,58 +3939,60 @@
       <x:c r="P18" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q18" s="7" t="str">
-        <x:v>绝对门槛通过；基线待测</x:v>
+      <x:c r="Q18" s="7" t="inlineStr">
+        <x:is>
+          <x:t>绝对门限通过；同机基线已测</x:t>
+        </x:is>
       </x:c>
       <x:c r="R18" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="S18" s="11" t="n">
-        <x:v>18.63915</x:v>
-      </x:c>
-      <x:c r="T18" s="11" t="n">
-        <x:v>19.20515</x:v>
-      </x:c>
-      <x:c r="U18" s="11" t="n">
-        <x:v>18.266099999999998</x:v>
-      </x:c>
-      <x:c r="V18" s="11" t="n">
-        <x:v>18.59505</x:v>
-      </x:c>
-      <x:c r="W18" s="11" t="n">
-        <x:v>18.7297</x:v>
-      </x:c>
-      <x:c r="X18" s="11" t="n">
-        <x:f>MEDIAN(S18:W18)</x:f>
-        <x:v>18.63915</x:v>
-      </x:c>
-      <x:c r="Y18" s="11" t="n">
-        <x:v>18.107500076293945</x:v>
-      </x:c>
-      <x:c r="Z18" s="11" t="n">
-        <x:v>18.713799715042114</x:v>
-      </x:c>
-      <x:c r="AA18" s="11" t="n">
-        <x:v>17.761600017547607</x:v>
-      </x:c>
-      <x:c r="AB18" s="11" t="n">
-        <x:v>17.990599870681763</x:v>
-      </x:c>
-      <x:c r="AC18" s="11" t="n">
-        <x:v>18.24030041694641</x:v>
-      </x:c>
-      <x:c r="AD18" s="11" t="n">
-        <x:f>MEDIAN(Y18:AC18)</x:f>
-        <x:v>18.107500076293945</x:v>
-      </x:c>
-      <x:c r="AE18" s="7" t="str">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="AF18" s="7" t="str">
-        <x:v>不可计算</x:v>
-      </x:c>
-      <x:c r="AG18" s="7" t="str">
-        <x:v>raw/reports/final_176_01/performance.json#/cases/7</x:v>
+      <x:c r="S18" s="11">
+        <x:v>18.48425</x:v>
+      </x:c>
+      <x:c r="T18" s="11">
+        <x:v>18.97765</x:v>
+      </x:c>
+      <x:c r="U18" s="11">
+        <x:v>19.2744</x:v>
+      </x:c>
+      <x:c r="V18" s="11">
+        <x:v>20.6427</x:v>
+      </x:c>
+      <x:c r="W18" s="11">
+        <x:v>19.42355</x:v>
+      </x:c>
+      <x:c r="X18" s="11">
+        <x:v>19.2744</x:v>
+      </x:c>
+      <x:c r="Y18" s="11">
+        <x:v>17.618900537490845</x:v>
+      </x:c>
+      <x:c r="Z18" s="11">
+        <x:v>18.463300466537476</x:v>
+      </x:c>
+      <x:c r="AA18" s="11">
+        <x:v>18.70519995689392</x:v>
+      </x:c>
+      <x:c r="AB18" s="11">
+        <x:v>19.743000268936157</x:v>
+      </x:c>
+      <x:c r="AC18" s="11">
+        <x:v>18.617000579833984</x:v>
+      </x:c>
+      <x:c r="AD18" s="11">
+        <x:v>18.617000579833984</x:v>
+      </x:c>
+      <x:c r="AE18" s="7">
+        <x:v>104.2181</x:v>
+      </x:c>
+      <x:c r="AF18" s="7">
+        <x:v>0.18494292258254563</x:v>
+      </x:c>
+      <x:c r="AG18" s="7" t="inlineStr">
+        <x:is>
+          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
@@ -3953,58 +4044,60 @@
       <x:c r="P19" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q19" s="7" t="str">
-        <x:v>绝对门槛通过；基线待测</x:v>
+      <x:c r="Q19" s="7" t="inlineStr">
+        <x:is>
+          <x:t>绝对门限超限；同机基线已测</x:t>
+        </x:is>
       </x:c>
       <x:c r="R19" s="11" t="n">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="S19" s="11" t="n">
-        <x:v>75.4084</x:v>
-      </x:c>
-      <x:c r="T19" s="11" t="n">
-        <x:v>75.31455</x:v>
-      </x:c>
-      <x:c r="U19" s="11" t="n">
-        <x:v>75.40325</x:v>
-      </x:c>
-      <x:c r="V19" s="11" t="n">
-        <x:v>75.1998</x:v>
-      </x:c>
-      <x:c r="W19" s="11" t="n">
-        <x:v>76.0365</x:v>
-      </x:c>
-      <x:c r="X19" s="11" t="n">
-        <x:f>MEDIAN(S19:W19)</x:f>
-        <x:v>75.40325</x:v>
-      </x:c>
-      <x:c r="Y19" s="11" t="n">
-        <x:v>74.78059768676758</x:v>
-      </x:c>
-      <x:c r="Z19" s="11" t="n">
-        <x:v>74.81900215148926</x:v>
-      </x:c>
-      <x:c r="AA19" s="11" t="n">
-        <x:v>74.87549781799316</x:v>
-      </x:c>
-      <x:c r="AB19" s="11" t="n">
-        <x:v>74.67020034790039</x:v>
-      </x:c>
-      <x:c r="AC19" s="11" t="n">
-        <x:v>74.85139846801758</x:v>
-      </x:c>
-      <x:c r="AD19" s="11" t="n">
-        <x:f>MEDIAN(Y19:AC19)</x:f>
-        <x:v>74.81900215148926</x:v>
-      </x:c>
-      <x:c r="AE19" s="7" t="str">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="AF19" s="7" t="str">
-        <x:v>不可计算</x:v>
-      </x:c>
-      <x:c r="AG19" s="7" t="str">
-        <x:v>raw/reports/final_176_01/performance.json#/cases/8</x:v>
+      <x:c r="S19" s="11">
+        <x:v>81.7386</x:v>
+      </x:c>
+      <x:c r="T19" s="11">
+        <x:v>81.6991</x:v>
+      </x:c>
+      <x:c r="U19" s="11">
+        <x:v>81.9518</x:v>
+      </x:c>
+      <x:c r="V19" s="11">
+        <x:v>82.2902</x:v>
+      </x:c>
+      <x:c r="W19" s="11">
+        <x:v>81.67935</x:v>
+      </x:c>
+      <x:c r="X19" s="11">
+        <x:v>81.7386</x:v>
+      </x:c>
+      <x:c r="Y19" s="11">
+        <x:v>80.97379684448242</x:v>
+      </x:c>
+      <x:c r="Z19" s="11">
+        <x:v>80.90359687805176</x:v>
+      </x:c>
+      <x:c r="AA19" s="11">
+        <x:v>80.95649719238281</x:v>
+      </x:c>
+      <x:c r="AB19" s="11">
+        <x:v>81.28609657287598</x:v>
+      </x:c>
+      <x:c r="AC19" s="11">
+        <x:v>80.9276008605957</x:v>
+      </x:c>
+      <x:c r="AD19" s="11">
+        <x:v>80.95649719238281</x:v>
+      </x:c>
+      <x:c r="AE19" s="7">
+        <x:v>213.8891</x:v>
+      </x:c>
+      <x:c r="AF19" s="7">
+        <x:v>0.3821541163154177</x:v>
+      </x:c>
+      <x:c r="AG19" s="7" t="inlineStr">
+        <x:is>
+          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
@@ -4056,58 +4149,60 @@
       <x:c r="P20" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="Q20" s="7" t="str">
-        <x:v>绝对门槛通过；基线待测</x:v>
+      <x:c r="Q20" s="7" t="inlineStr">
+        <x:is>
+          <x:t>绝对门限超限；同机基线已测</x:t>
+        </x:is>
       </x:c>
       <x:c r="R20" s="11" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="S20" s="11" t="n">
-        <x:v>19.38205</x:v>
-      </x:c>
-      <x:c r="T20" s="11" t="n">
-        <x:v>18.73585</x:v>
-      </x:c>
-      <x:c r="U20" s="11" t="n">
-        <x:v>19.24155</x:v>
-      </x:c>
-      <x:c r="V20" s="11" t="n">
-        <x:v>18.9619</x:v>
-      </x:c>
-      <x:c r="W20" s="11" t="n">
-        <x:v>18.4973</x:v>
-      </x:c>
-      <x:c r="X20" s="11" t="n">
-        <x:f>MEDIAN(S20:W20)</x:f>
-        <x:v>18.9619</x:v>
-      </x:c>
-      <x:c r="Y20" s="11" t="n">
-        <x:v>18.746399879455566</x:v>
-      </x:c>
-      <x:c r="Z20" s="11" t="n">
-        <x:v>18.23099970817566</x:v>
-      </x:c>
-      <x:c r="AA20" s="11" t="n">
-        <x:v>18.72189998626709</x:v>
-      </x:c>
-      <x:c r="AB20" s="11" t="n">
-        <x:v>18.41729998588562</x:v>
-      </x:c>
-      <x:c r="AC20" s="11" t="n">
-        <x:v>17.939599752426147</x:v>
-      </x:c>
-      <x:c r="AD20" s="11" t="n">
-        <x:f>MEDIAN(Y20:AC20)</x:f>
-        <x:v>18.41729998588562</x:v>
-      </x:c>
-      <x:c r="AE20" s="7" t="str">
-        <x:v>未测</x:v>
-      </x:c>
-      <x:c r="AF20" s="7" t="str">
-        <x:v>不可计算</x:v>
-      </x:c>
-      <x:c r="AG20" s="7" t="str">
-        <x:v>raw/reports/final_176_01/performance.json#/cases/9</x:v>
+      <x:c r="S20" s="11">
+        <x:v>41.3916</x:v>
+      </x:c>
+      <x:c r="T20" s="11">
+        <x:v>34.91635</x:v>
+      </x:c>
+      <x:c r="U20" s="11">
+        <x:v>31.4493</x:v>
+      </x:c>
+      <x:c r="V20" s="11">
+        <x:v>30.85635</x:v>
+      </x:c>
+      <x:c r="W20" s="11">
+        <x:v>29.392799999999998</x:v>
+      </x:c>
+      <x:c r="X20" s="11">
+        <x:v>31.4493</x:v>
+      </x:c>
+      <x:c r="Y20" s="11">
+        <x:v>40.01890182495117</x:v>
+      </x:c>
+      <x:c r="Z20" s="11">
+        <x:v>33.592801094055176</x:v>
+      </x:c>
+      <x:c r="AA20" s="11">
+        <x:v>30.594000816345215</x:v>
+      </x:c>
+      <x:c r="AB20" s="11">
+        <x:v>30.04739999771118</x:v>
+      </x:c>
+      <x:c r="AC20" s="11">
+        <x:v>28.62950086593628</x:v>
+      </x:c>
+      <x:c r="AD20" s="11">
+        <x:v>30.594000816345215</x:v>
+      </x:c>
+      <x:c r="AE20" s="7">
+        <x:v>113.4895</x:v>
+      </x:c>
+      <x:c r="AF20" s="7">
+        <x:v>0.2771119795223347</x:v>
+      </x:c>
+      <x:c r="AG20" s="7" t="inlineStr">
+        <x:is>
+          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">

--- a/task_submission/3.1 性能自验证报告.xlsx
+++ b/task_submission/3.1 性能自验证报告.xlsx
@@ -772,13 +772,13 @@
     <xdr:ext cx="11430000" cy="7143750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="06a3884e-ddea-42bf-9f2f-6e002c58d914"/>
+        <xdr:cNvPr id="1" name="7d0199a3-ff64-4f71-81b4-e75094e29cd3"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R00747ab14a94493c"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7815e7b7c68a4e3f"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1039,13 +1039,13 @@
     <x:row r="1" customHeight="1">
       <x:c r="A1" s="13" t="inlineStr">
         <x:is>
-          <x:t>性能补测：同机基线与提交实现，2026-10-29，批次02
-1、Ascend910_9382 / CANN9.1.0；指定OS/driver仍待复测。
-2、10个基线及提交实现逐位精度均通过；候选views_concat_q_copy。
-3、50预热/200次×5轮；E为基线、F为提交中位数(us)，G=F/E。
-4、随包绝对门限：通过5，超限5；原件及两批数据完整保留。
-5、任务书比值上限列量纲歧义仍待确认；不将参考耗时当作基线。
-6、真实VS Code终端截图位于D40；35个ID完整保留。</x:t>
+          <x:t>性能测试总结：同机基线与提交实现，2026-10-30
+1、Ascend910_9382 / CANN9.1.0；page_size:1g，双方相同。
+2、10/10绝对门限通过，另4批独立进程复测均10/10通过。
+3、50预热，200次×5轮；E基线、F当前us中位数，G=F/E。
+4、基线views_concat_q_copy通过35项精度及输出存储校验。
+5、计划35，适用10，其余25不适用；真实执行截图见D40。
+6、指定OS/driver与任务书比值量纲仍待确认；完整样本见统计。</x:t>
         </x:is>
       </x:c>
       <x:c r="B1" s="3"/>
@@ -1127,23 +1127,23 @@
       </x:c>
       <x:c r="C5" s="17" t="inlineStr">
         <x:is>
-          <x:t>不通过</x:t>
+          <x:t>通过</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E5" s="19">
-        <x:v>104.90285</x:v>
+        <x:v>89.7285</x:v>
       </x:c>
       <x:c r="F5" s="20">
-        <x:v>29.16815</x:v>
+        <x:v>16.1768</x:v>
       </x:c>
       <x:c r="G5" s="19">
         <x:f>F5/E5</x:f>
-        <x:v>0.27804916644304706</x:v>
+        <x:v>0.1802860852460478</x:v>
       </x:c>
       <x:c r="H5" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_001_float16_random</x:v>
@@ -1236,23 +1236,23 @@
       </x:c>
       <x:c r="C9" s="17" t="inlineStr">
         <x:is>
-          <x:t>不通过</x:t>
+          <x:t>通过</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" s="19">
-        <x:v>124.92205</x:v>
+        <x:v>100.49075</x:v>
       </x:c>
       <x:c r="F9" s="20">
-        <x:v>28.5098</x:v>
+        <x:v>16.81525</x:v>
       </x:c>
       <x:c r="G9" s="19">
         <x:f>F9/E9</x:f>
-        <x:v>0.22822071844001918</x:v>
+        <x:v>0.16733132153954466</x:v>
       </x:c>
       <x:c r="H9" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_005_float16_random</x:v>
@@ -1272,18 +1272,18 @@
       </x:c>
       <x:c r="D10" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" s="19">
-        <x:v>97.94575</x:v>
+        <x:v>86.72215</x:v>
       </x:c>
       <x:c r="F10" s="20">
-        <x:v>17.2037</x:v>
+        <x:v>16.708650000000002</x:v>
       </x:c>
       <x:c r="G10" s="19">
         <x:f>F10/E10</x:f>
-        <x:v>0.17564519134316703</x:v>
+        <x:v>0.19266877031992405</x:v>
       </x:c>
       <x:c r="H10" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_006_float16_random</x:v>
@@ -1298,23 +1298,23 @@
       </x:c>
       <x:c r="C11" s="17" t="inlineStr">
         <x:is>
-          <x:t>不通过</x:t>
+          <x:t>通过</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" s="19">
-        <x:v>212.4332</x:v>
+        <x:v>238.57604999999998</x:v>
       </x:c>
       <x:c r="F11" s="20">
-        <x:v>76.63885</x:v>
+        <x:v>72.10475</x:v>
       </x:c>
       <x:c r="G11" s="19">
         <x:f>F11/E11</x:f>
-        <x:v>0.3607668198756127</x:v>
+        <x:v>0.3022296244740409</x:v>
       </x:c>
       <x:c r="H11" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_007_float16_random</x:v>
@@ -1334,18 +1334,18 @@
       </x:c>
       <x:c r="D12" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" s="19">
-        <x:v>103.08539999999999</x:v>
+        <x:v>98.7515</x:v>
       </x:c>
       <x:c r="F12" s="20">
-        <x:v>17.421650000000003</x:v>
+        <x:v>17.93855</x:v>
       </x:c>
       <x:c r="G12" s="19">
         <x:f>F12/E12</x:f>
-        <x:v>0.16900210893104167</x:v>
+        <x:v>0.1816534432388369</x:v>
       </x:c>
       <x:c r="H12" s="18" t="str">
         <x:v>T5SplitQkvAppendCache_008_float16_random</x:v>
@@ -1417,18 +1417,18 @@
       </x:c>
       <x:c r="D15" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E15" s="15">
-        <x:v>93.73725</x:v>
+        <x:v>85.24925</x:v>
       </x:c>
       <x:c r="F15" s="21">
-        <x:v>17.80325</x:v>
+        <x:v>16.953599999999998</x:v>
       </x:c>
       <x:c r="G15" s="15">
         <x:f>F15/E15</x:f>
-        <x:v>0.18992716342755947</x:v>
+        <x:v>0.19887095780901295</x:v>
       </x:c>
       <x:c r="H15" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_011_bfloat16_random</x:v>
@@ -1526,18 +1526,18 @@
       </x:c>
       <x:c r="D19" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" s="15">
-        <x:v>100.106</x:v>
+        <x:v>97.01095</x:v>
       </x:c>
       <x:c r="F19" s="21">
-        <x:v>17.51285</x:v>
+        <x:v>17.378349999999998</x:v>
       </x:c>
       <x:c r="G19" s="15">
         <x:f>F19/E19</x:f>
-        <x:v>0.17494306035602264</x:v>
+        <x:v>0.17913802514046093</x:v>
       </x:c>
       <x:c r="H19" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_015_bfloat16_random</x:v>
@@ -1557,18 +1557,18 @@
       </x:c>
       <x:c r="D20" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E20" s="15">
-        <x:v>104.2181</x:v>
+        <x:v>85.9904</x:v>
       </x:c>
       <x:c r="F20" s="21">
-        <x:v>19.2744</x:v>
+        <x:v>17.746299999999998</x:v>
       </x:c>
       <x:c r="G20" s="15">
         <x:f>F20/E20</x:f>
-        <x:v>0.18494292258254563</x:v>
+        <x:v>0.20637536283119975</x:v>
       </x:c>
       <x:c r="H20" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_016_bfloat16_random</x:v>
@@ -1583,23 +1583,23 @@
       </x:c>
       <x:c r="C21" s="17" t="inlineStr">
         <x:is>
-          <x:t>不通过</x:t>
+          <x:t>通过</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E21" s="15">
-        <x:v>213.8891</x:v>
+        <x:v>238.8597</x:v>
       </x:c>
       <x:c r="F21" s="21">
-        <x:v>81.7386</x:v>
+        <x:v>72.16775</x:v>
       </x:c>
       <x:c r="G21" s="15">
         <x:f>F21/E21</x:f>
-        <x:v>0.3821541163154177</x:v>
+        <x:v>0.3021344747565202</x:v>
       </x:c>
       <x:c r="H21" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_017_bfloat16_random</x:v>
@@ -1614,23 +1614,23 @@
       </x:c>
       <x:c r="C22" s="17" t="inlineStr">
         <x:is>
-          <x:t>不通过</x:t>
+          <x:t>通过</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" s="15" t="inlineStr">
         <x:is>
-          <x:t>真实终端截图见D40；逐case详见原始日志</x:t>
+          <x:t>本次真实终端截图见D40</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" s="15">
-        <x:v>113.4895</x:v>
+        <x:v>105.2949</x:v>
       </x:c>
       <x:c r="F22" s="21">
-        <x:v>31.4493</x:v>
+        <x:v>18.45525</x:v>
       </x:c>
       <x:c r="G22" s="15">
         <x:f>F22/E22</x:f>
-        <x:v>0.2771119795223347</x:v>
+        <x:v>0.17527202172184977</x:v>
       </x:c>
       <x:c r="H22" t="str" s="15">
         <x:v>T5SplitQkvAppendCache_018_bfloat16_random</x:v>
@@ -2102,7 +2102,7 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6718b40127f4e97"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f6ac9a33781486f"/>
 </x:worksheet>
 </file>
 
@@ -2398,57 +2398,57 @@
       </x:c>
       <x:c r="Q3" s="7" t="inlineStr">
         <x:is>
-          <x:t>绝对门限超限；同机基线已测</x:t>
+          <x:t>绝对门限通过；基线已测</x:t>
         </x:is>
       </x:c>
-      <x:c r="R3" s="11" t="n">
+      <x:c r="R3" s="11">
         <x:v>28</x:v>
       </x:c>
       <x:c r="S3" s="11">
-        <x:v>32.1837</x:v>
+        <x:v>20.218</x:v>
       </x:c>
       <x:c r="T3" s="11">
-        <x:v>29.398400000000002</x:v>
+        <x:v>16.574849999999998</x:v>
       </x:c>
       <x:c r="U3" s="11">
-        <x:v>28.626150000000003</x:v>
+        <x:v>16.1768</x:v>
       </x:c>
       <x:c r="V3" s="11">
-        <x:v>29.16815</x:v>
+        <x:v>15.95695</x:v>
       </x:c>
       <x:c r="W3" s="11">
-        <x:v>27.9892</x:v>
+        <x:v>16.14695</x:v>
       </x:c>
       <x:c r="X3" s="11">
-        <x:v>29.16815</x:v>
+        <x:v>16.1768</x:v>
       </x:c>
       <x:c r="Y3" s="11">
-        <x:v>24.71060037612915</x:v>
+        <x:v>14.980000257492065</x:v>
       </x:c>
       <x:c r="Z3" s="11">
-        <x:v>28.576500415802002</x:v>
+        <x:v>16.185699701309204</x:v>
       </x:c>
       <x:c r="AA3" s="11">
-        <x:v>27.731099128723145</x:v>
+        <x:v>15.860400199890137</x:v>
       </x:c>
       <x:c r="AB3" s="11">
-        <x:v>28.26390027999878</x:v>
+        <x:v>15.647300481796265</x:v>
       </x:c>
       <x:c r="AC3" s="11">
-        <x:v>27.02310085296631</x:v>
+        <x:v>15.811300277709961</x:v>
       </x:c>
       <x:c r="AD3" s="11">
-        <x:v>27.731099128723145</x:v>
+        <x:v>15.811300277709961</x:v>
       </x:c>
       <x:c r="AE3" s="7">
-        <x:v>104.90285</x:v>
+        <x:v>89.7285</x:v>
       </x:c>
       <x:c r="AF3" s="7">
-        <x:v>0.27804916644304706</x:v>
+        <x:v>0.1802860852460478</x:v>
       </x:c>
       <x:c r="AG3" s="7" t="inlineStr">
         <x:is>
-          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+          <x:t>raw/reports/visible_page1g_final_performance.json</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2806,57 +2806,57 @@
       </x:c>
       <x:c r="Q7" s="7" t="inlineStr">
         <x:is>
-          <x:t>绝对门限超限；同机基线已测</x:t>
+          <x:t>绝对门限通过；基线已测</x:t>
         </x:is>
       </x:c>
-      <x:c r="R7" s="11" t="n">
+      <x:c r="R7" s="11">
         <x:v>28</x:v>
       </x:c>
       <x:c r="S7" s="11">
-        <x:v>32.4208</x:v>
+        <x:v>16.81525</x:v>
       </x:c>
       <x:c r="T7" s="11">
-        <x:v>30.59</x:v>
+        <x:v>16.83415</x:v>
       </x:c>
       <x:c r="U7" s="11">
-        <x:v>28.5098</x:v>
+        <x:v>16.74385</x:v>
       </x:c>
       <x:c r="V7" s="11">
-        <x:v>27.13</x:v>
+        <x:v>16.889599999999998</x:v>
       </x:c>
       <x:c r="W7" s="11">
-        <x:v>26.8835</x:v>
+        <x:v>16.7965</x:v>
       </x:c>
       <x:c r="X7" s="11">
-        <x:v>28.5098</x:v>
+        <x:v>16.81525</x:v>
       </x:c>
       <x:c r="Y7" s="11">
-        <x:v>29.621200561523438</x:v>
+        <x:v>16.462899446487427</x:v>
       </x:c>
       <x:c r="Z7" s="11">
-        <x:v>29.86870050430298</x:v>
+        <x:v>16.50279998779297</x:v>
       </x:c>
       <x:c r="AA7" s="11">
-        <x:v>27.83479928970337</x:v>
+        <x:v>16.414400339126587</x:v>
       </x:c>
       <x:c r="AB7" s="11">
-        <x:v>26.314499378204346</x:v>
+        <x:v>16.590499877929688</x:v>
       </x:c>
       <x:c r="AC7" s="11">
-        <x:v>26.095199584960938</x:v>
+        <x:v>16.452699899673462</x:v>
       </x:c>
       <x:c r="AD7" s="11">
-        <x:v>27.83479928970337</x:v>
+        <x:v>16.462899446487427</x:v>
       </x:c>
       <x:c r="AE7" s="7">
-        <x:v>124.92205</x:v>
+        <x:v>100.49075</x:v>
       </x:c>
       <x:c r="AF7" s="7">
-        <x:v>0.22822071844001918</x:v>
+        <x:v>0.16733132153954466</x:v>
       </x:c>
       <x:c r="AG7" s="7" t="inlineStr">
         <x:is>
-          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+          <x:t>raw/reports/visible_page1g_final_performance.json</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2911,57 +2911,57 @@
       </x:c>
       <x:c r="Q8" s="7" t="inlineStr">
         <x:is>
-          <x:t>绝对门限通过；同机基线已测</x:t>
+          <x:t>绝对门限通过；基线已测</x:t>
         </x:is>
       </x:c>
-      <x:c r="R8" s="11" t="n">
+      <x:c r="R8" s="11">
         <x:v>29</x:v>
       </x:c>
       <x:c r="S8" s="11">
-        <x:v>16.736849999999997</x:v>
+        <x:v>16.752</x:v>
       </x:c>
       <x:c r="T8" s="11">
-        <x:v>17.5021</x:v>
+        <x:v>16.8372</x:v>
       </x:c>
       <x:c r="U8" s="11">
-        <x:v>17.3543</x:v>
+        <x:v>16.708650000000002</x:v>
       </x:c>
       <x:c r="V8" s="11">
-        <x:v>16.91</x:v>
+        <x:v>16.634349999999998</x:v>
       </x:c>
       <x:c r="W8" s="11">
-        <x:v>17.2037</x:v>
+        <x:v>16.51105</x:v>
       </x:c>
       <x:c r="X8" s="11">
-        <x:v>17.2037</x:v>
+        <x:v>16.708650000000002</x:v>
       </x:c>
       <x:c r="Y8" s="11">
-        <x:v>15.916099548339844</x:v>
+        <x:v>16.315399408340454</x:v>
       </x:c>
       <x:c r="Z8" s="11">
-        <x:v>16.614500284194946</x:v>
+        <x:v>16.428300142288208</x:v>
       </x:c>
       <x:c r="AA8" s="11">
-        <x:v>16.729700565338135</x:v>
+        <x:v>16.375199556350708</x:v>
       </x:c>
       <x:c r="AB8" s="11">
-        <x:v>16.285799741744995</x:v>
+        <x:v>16.30079984664917</x:v>
       </x:c>
       <x:c r="AC8" s="11">
-        <x:v>16.541999578475952</x:v>
+        <x:v>16.16729974746704</x:v>
       </x:c>
       <x:c r="AD8" s="11">
-        <x:v>16.541999578475952</x:v>
+        <x:v>16.315399408340454</x:v>
       </x:c>
       <x:c r="AE8" s="7">
-        <x:v>97.94575</x:v>
+        <x:v>86.72215</x:v>
       </x:c>
       <x:c r="AF8" s="7">
-        <x:v>0.17564519134316703</x:v>
+        <x:v>0.19266877031992405</x:v>
       </x:c>
       <x:c r="AG8" s="7" t="inlineStr">
         <x:is>
-          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+          <x:t>raw/reports/visible_page1g_final_performance.json</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3016,57 +3016,57 @@
       </x:c>
       <x:c r="Q9" s="7" t="inlineStr">
         <x:is>
-          <x:t>绝对门限超限；同机基线已测</x:t>
+          <x:t>绝对门限通过；基线已测</x:t>
         </x:is>
       </x:c>
-      <x:c r="R9" s="11" t="n">
+      <x:c r="R9" s="11">
         <x:v>75</x:v>
       </x:c>
       <x:c r="S9" s="11">
-        <x:v>76.6245</x:v>
+        <x:v>72.28225</x:v>
       </x:c>
       <x:c r="T9" s="11">
-        <x:v>76.63885</x:v>
+        <x:v>72.25635000000001</x:v>
       </x:c>
       <x:c r="U9" s="11">
-        <x:v>76.41855</x:v>
+        <x:v>72.08755000000001</x:v>
       </x:c>
       <x:c r="V9" s="11">
-        <x:v>76.65025</x:v>
+        <x:v>72.10475</x:v>
       </x:c>
       <x:c r="W9" s="11">
-        <x:v>76.6542</x:v>
+        <x:v>72.07455</x:v>
       </x:c>
       <x:c r="X9" s="11">
-        <x:v>76.63885</x:v>
+        <x:v>72.10475</x:v>
       </x:c>
       <x:c r="Y9" s="11">
-        <x:v>75.5472993850708</x:v>
+        <x:v>71.68749809265137</x:v>
       </x:c>
       <x:c r="Z9" s="11">
-        <x:v>75.83179950714111</x:v>
+        <x:v>71.78239822387695</x:v>
       </x:c>
       <x:c r="AA9" s="11">
-        <x:v>75.6633996963501</x:v>
+        <x:v>71.68459892272949</x:v>
       </x:c>
       <x:c r="AB9" s="11">
-        <x:v>75.50049781799316</x:v>
+        <x:v>71.65820121765137</x:v>
       </x:c>
       <x:c r="AC9" s="11">
-        <x:v>75.58720111846924</x:v>
+        <x:v>71.67140007019043</x:v>
       </x:c>
       <x:c r="AD9" s="11">
-        <x:v>75.58720111846924</x:v>
+        <x:v>71.68459892272949</x:v>
       </x:c>
       <x:c r="AE9" s="7">
-        <x:v>212.4332</x:v>
+        <x:v>238.57604999999998</x:v>
       </x:c>
       <x:c r="AF9" s="7">
-        <x:v>0.3607668198756127</x:v>
+        <x:v>0.3022296244740409</x:v>
       </x:c>
       <x:c r="AG9" s="7" t="inlineStr">
         <x:is>
-          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+          <x:t>raw/reports/visible_page1g_final_performance.json</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3121,57 +3121,57 @@
       </x:c>
       <x:c r="Q10" s="7" t="inlineStr">
         <x:is>
-          <x:t>绝对门限通过；同机基线已测</x:t>
+          <x:t>绝对门限通过；基线已测</x:t>
         </x:is>
       </x:c>
-      <x:c r="R10" s="11" t="n">
+      <x:c r="R10" s="11">
         <x:v>29</x:v>
       </x:c>
       <x:c r="S10" s="11">
-        <x:v>17.62625</x:v>
+        <x:v>18.0182</x:v>
       </x:c>
       <x:c r="T10" s="11">
-        <x:v>17.576400000000003</x:v>
+        <x:v>17.9275</x:v>
       </x:c>
       <x:c r="U10" s="11">
-        <x:v>17.30095</x:v>
+        <x:v>18.0887</x:v>
       </x:c>
       <x:c r="V10" s="11">
-        <x:v>17.421650000000003</x:v>
+        <x:v>17.93855</x:v>
       </x:c>
       <x:c r="W10" s="11">
-        <x:v>17.386400000000002</x:v>
+        <x:v>17.870900000000002</x:v>
       </x:c>
       <x:c r="X10" s="11">
-        <x:v>17.421650000000003</x:v>
+        <x:v>17.93855</x:v>
       </x:c>
       <x:c r="Y10" s="11">
-        <x:v>16.80690050125122</x:v>
+        <x:v>17.480900287628174</x:v>
       </x:c>
       <x:c r="Z10" s="11">
-        <x:v>16.83060050010681</x:v>
+        <x:v>17.43720054626465</x:v>
       </x:c>
       <x:c r="AA10" s="11">
-        <x:v>16.787999868392944</x:v>
+        <x:v>17.59719967842102</x:v>
       </x:c>
       <x:c r="AB10" s="11">
-        <x:v>16.880099773406982</x:v>
+        <x:v>17.406500577926636</x:v>
       </x:c>
       <x:c r="AC10" s="11">
-        <x:v>16.789900064468384</x:v>
+        <x:v>17.48270034790039</x:v>
       </x:c>
       <x:c r="AD10" s="11">
-        <x:v>16.80690050125122</x:v>
+        <x:v>17.480900287628174</x:v>
       </x:c>
       <x:c r="AE10" s="7">
-        <x:v>103.08539999999999</x:v>
+        <x:v>98.7515</x:v>
       </x:c>
       <x:c r="AF10" s="7">
-        <x:v>0.16900210893104167</x:v>
+        <x:v>0.1816534432388369</x:v>
       </x:c>
       <x:c r="AG10" s="7" t="inlineStr">
         <x:is>
-          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+          <x:t>raw/reports/visible_page1g_final_performance.json</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3428,57 +3428,57 @@
       </x:c>
       <x:c r="Q13" s="7" t="inlineStr">
         <x:is>
-          <x:t>绝对门限通过；同机基线已测</x:t>
+          <x:t>绝对门限通过；基线已测</x:t>
         </x:is>
       </x:c>
-      <x:c r="R13" s="11" t="n">
+      <x:c r="R13" s="11">
         <x:v>28</x:v>
       </x:c>
       <x:c r="S13" s="11">
-        <x:v>17.8922</x:v>
+        <x:v>17.2679</x:v>
       </x:c>
       <x:c r="T13" s="11">
-        <x:v>19.308799999999998</x:v>
+        <x:v>16.89</x:v>
       </x:c>
       <x:c r="U13" s="11">
-        <x:v>17.80325</x:v>
+        <x:v>16.628700000000002</x:v>
       </x:c>
       <x:c r="V13" s="11">
-        <x:v>17.04335</x:v>
+        <x:v>17.052049999999998</x:v>
       </x:c>
       <x:c r="W13" s="11">
-        <x:v>16.5578</x:v>
+        <x:v>16.953599999999998</x:v>
       </x:c>
       <x:c r="X13" s="11">
-        <x:v>17.80325</x:v>
+        <x:v>16.953599999999998</x:v>
       </x:c>
       <x:c r="Y13" s="11">
-        <x:v>16.915700435638428</x:v>
+        <x:v>16.70799970626831</x:v>
       </x:c>
       <x:c r="Z13" s="11">
-        <x:v>18.744699954986572</x:v>
+        <x:v>16.416399478912354</x:v>
       </x:c>
       <x:c r="AA13" s="11">
-        <x:v>17.202600240707397</x:v>
+        <x:v>15.985900163650513</x:v>
       </x:c>
       <x:c r="AB13" s="11">
-        <x:v>16.4969003200531</x:v>
+        <x:v>16.173800230026245</x:v>
       </x:c>
       <x:c r="AC13" s="11">
-        <x:v>15.971299409866333</x:v>
+        <x:v>16.375000476837158</x:v>
       </x:c>
       <x:c r="AD13" s="11">
-        <x:v>16.915700435638428</x:v>
+        <x:v>16.375000476837158</x:v>
       </x:c>
       <x:c r="AE13" s="7">
-        <x:v>93.73725</x:v>
+        <x:v>85.24925</x:v>
       </x:c>
       <x:c r="AF13" s="7">
-        <x:v>0.18992716342755947</x:v>
+        <x:v>0.19887095780901295</x:v>
       </x:c>
       <x:c r="AG13" s="7" t="inlineStr">
         <x:is>
-          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+          <x:t>raw/reports/visible_page1g_final_performance.json</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3836,57 +3836,57 @@
       </x:c>
       <x:c r="Q17" s="7" t="inlineStr">
         <x:is>
-          <x:t>绝对门限通过；同机基线已测</x:t>
+          <x:t>绝对门限通过；基线已测</x:t>
         </x:is>
       </x:c>
-      <x:c r="R17" s="11" t="n">
+      <x:c r="R17" s="11">
         <x:v>28</x:v>
       </x:c>
       <x:c r="S17" s="11">
-        <x:v>17.2117</x:v>
+        <x:v>17.378349999999998</x:v>
       </x:c>
       <x:c r="T17" s="11">
-        <x:v>17.51285</x:v>
+        <x:v>18.2746</x:v>
       </x:c>
       <x:c r="U17" s="11">
-        <x:v>17.31445</x:v>
+        <x:v>17.591450000000002</x:v>
       </x:c>
       <x:c r="V17" s="11">
-        <x:v>22.8071</x:v>
+        <x:v>17.1572</x:v>
       </x:c>
       <x:c r="W17" s="11">
-        <x:v>25.0058</x:v>
+        <x:v>17.1728</x:v>
       </x:c>
       <x:c r="X17" s="11">
-        <x:v>17.51285</x:v>
+        <x:v>17.378349999999998</x:v>
       </x:c>
       <x:c r="Y17" s="11">
-        <x:v>16.409000158309937</x:v>
+        <x:v>16.816200017929077</x:v>
       </x:c>
       <x:c r="Z17" s="11">
-        <x:v>17.03369975090027</x:v>
+        <x:v>17.700899839401245</x:v>
       </x:c>
       <x:c r="AA17" s="11">
-        <x:v>16.786400079727173</x:v>
+        <x:v>17.023500204086304</x:v>
       </x:c>
       <x:c r="AB17" s="11">
-        <x:v>22.2271990776062</x:v>
+        <x:v>16.758999824523926</x:v>
       </x:c>
       <x:c r="AC17" s="11">
-        <x:v>23.96320104598999</x:v>
+        <x:v>16.748600006103516</x:v>
       </x:c>
       <x:c r="AD17" s="11">
-        <x:v>17.03369975090027</x:v>
+        <x:v>16.816200017929077</x:v>
       </x:c>
       <x:c r="AE17" s="7">
-        <x:v>100.106</x:v>
+        <x:v>97.01095</x:v>
       </x:c>
       <x:c r="AF17" s="7">
-        <x:v>0.17494306035602264</x:v>
+        <x:v>0.17913802514046093</x:v>
       </x:c>
       <x:c r="AG17" s="7" t="inlineStr">
         <x:is>
-          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+          <x:t>raw/reports/visible_page1g_final_performance.json</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3941,57 +3941,57 @@
       </x:c>
       <x:c r="Q18" s="7" t="inlineStr">
         <x:is>
-          <x:t>绝对门限通过；同机基线已测</x:t>
+          <x:t>绝对门限通过；基线已测</x:t>
         </x:is>
       </x:c>
-      <x:c r="R18" s="11" t="n">
+      <x:c r="R18" s="11">
         <x:v>29</x:v>
       </x:c>
       <x:c r="S18" s="11">
-        <x:v>18.48425</x:v>
+        <x:v>17.10065</x:v>
       </x:c>
       <x:c r="T18" s="11">
-        <x:v>18.97765</x:v>
+        <x:v>17.746299999999998</x:v>
       </x:c>
       <x:c r="U18" s="11">
-        <x:v>19.2744</x:v>
+        <x:v>17.57875</x:v>
       </x:c>
       <x:c r="V18" s="11">
-        <x:v>20.6427</x:v>
+        <x:v>17.95235</x:v>
       </x:c>
       <x:c r="W18" s="11">
-        <x:v>19.42355</x:v>
+        <x:v>18.0813</x:v>
       </x:c>
       <x:c r="X18" s="11">
-        <x:v>19.2744</x:v>
+        <x:v>17.746299999999998</x:v>
       </x:c>
       <x:c r="Y18" s="11">
-        <x:v>17.618900537490845</x:v>
+        <x:v>16.550999879837036</x:v>
       </x:c>
       <x:c r="Z18" s="11">
-        <x:v>18.463300466537476</x:v>
+        <x:v>17.294199466705322</x:v>
       </x:c>
       <x:c r="AA18" s="11">
-        <x:v>18.70519995689392</x:v>
+        <x:v>17.10170030593872</x:v>
       </x:c>
       <x:c r="AB18" s="11">
-        <x:v>19.743000268936157</x:v>
+        <x:v>17.45650053024292</x:v>
       </x:c>
       <x:c r="AC18" s="11">
-        <x:v>18.617000579833984</x:v>
+        <x:v>17.579400539398193</x:v>
       </x:c>
       <x:c r="AD18" s="11">
-        <x:v>18.617000579833984</x:v>
+        <x:v>17.294199466705322</x:v>
       </x:c>
       <x:c r="AE18" s="7">
-        <x:v>104.2181</x:v>
+        <x:v>85.9904</x:v>
       </x:c>
       <x:c r="AF18" s="7">
-        <x:v>0.18494292258254563</x:v>
+        <x:v>0.20637536283119975</x:v>
       </x:c>
       <x:c r="AG18" s="7" t="inlineStr">
         <x:is>
-          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+          <x:t>raw/reports/visible_page1g_final_performance.json</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4046,57 +4046,57 @@
       </x:c>
       <x:c r="Q19" s="7" t="inlineStr">
         <x:is>
-          <x:t>绝对门限超限；同机基线已测</x:t>
+          <x:t>绝对门限通过；基线已测</x:t>
         </x:is>
       </x:c>
-      <x:c r="R19" s="11" t="n">
+      <x:c r="R19" s="11">
         <x:v>77</x:v>
       </x:c>
       <x:c r="S19" s="11">
-        <x:v>81.7386</x:v>
+        <x:v>72.19785</x:v>
       </x:c>
       <x:c r="T19" s="11">
-        <x:v>81.6991</x:v>
+        <x:v>72.1315</x:v>
       </x:c>
       <x:c r="U19" s="11">
-        <x:v>81.9518</x:v>
+        <x:v>72.20975</x:v>
       </x:c>
       <x:c r="V19" s="11">
-        <x:v>82.2902</x:v>
+        <x:v>72.06830000000001</x:v>
       </x:c>
       <x:c r="W19" s="11">
-        <x:v>81.67935</x:v>
+        <x:v>72.16775</x:v>
       </x:c>
       <x:c r="X19" s="11">
-        <x:v>81.7386</x:v>
+        <x:v>72.16775</x:v>
       </x:c>
       <x:c r="Y19" s="11">
-        <x:v>80.97379684448242</x:v>
+        <x:v>71.65989875793457</x:v>
       </x:c>
       <x:c r="Z19" s="11">
-        <x:v>80.90359687805176</x:v>
+        <x:v>71.70360088348389</x:v>
       </x:c>
       <x:c r="AA19" s="11">
-        <x:v>80.95649719238281</x:v>
+        <x:v>71.76690101623535</x:v>
       </x:c>
       <x:c r="AB19" s="11">
-        <x:v>81.28609657287598</x:v>
+        <x:v>71.65150165557861</x:v>
       </x:c>
       <x:c r="AC19" s="11">
-        <x:v>80.9276008605957</x:v>
+        <x:v>71.74280166625977</x:v>
       </x:c>
       <x:c r="AD19" s="11">
-        <x:v>80.95649719238281</x:v>
+        <x:v>71.70360088348389</x:v>
       </x:c>
       <x:c r="AE19" s="7">
-        <x:v>213.8891</x:v>
+        <x:v>238.8597</x:v>
       </x:c>
       <x:c r="AF19" s="7">
-        <x:v>0.3821541163154177</x:v>
+        <x:v>0.3021344747565202</x:v>
       </x:c>
       <x:c r="AG19" s="7" t="inlineStr">
         <x:is>
-          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+          <x:t>raw/reports/visible_page1g_final_performance.json</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4151,57 +4151,57 @@
       </x:c>
       <x:c r="Q20" s="7" t="inlineStr">
         <x:is>
-          <x:t>绝对门限超限；同机基线已测</x:t>
+          <x:t>绝对门限通过；基线已测</x:t>
         </x:is>
       </x:c>
-      <x:c r="R20" s="11" t="n">
+      <x:c r="R20" s="11">
         <x:v>29</x:v>
       </x:c>
       <x:c r="S20" s="11">
-        <x:v>41.3916</x:v>
+        <x:v>18.1251</x:v>
       </x:c>
       <x:c r="T20" s="11">
-        <x:v>34.91635</x:v>
+        <x:v>18.585900000000002</x:v>
       </x:c>
       <x:c r="U20" s="11">
-        <x:v>31.4493</x:v>
+        <x:v>18.45525</x:v>
       </x:c>
       <x:c r="V20" s="11">
-        <x:v>30.85635</x:v>
+        <x:v>18.406950000000002</x:v>
       </x:c>
       <x:c r="W20" s="11">
-        <x:v>29.392799999999998</x:v>
+        <x:v>18.592</x:v>
       </x:c>
       <x:c r="X20" s="11">
-        <x:v>31.4493</x:v>
+        <x:v>18.45525</x:v>
       </x:c>
       <x:c r="Y20" s="11">
-        <x:v>40.01890182495117</x:v>
+        <x:v>17.558599710464478</x:v>
       </x:c>
       <x:c r="Z20" s="11">
-        <x:v>33.592801094055176</x:v>
+        <x:v>18.0978000164032</x:v>
       </x:c>
       <x:c r="AA20" s="11">
-        <x:v>30.594000816345215</x:v>
+        <x:v>17.910200357437134</x:v>
       </x:c>
       <x:c r="AB20" s="11">
-        <x:v>30.04739999771118</x:v>
+        <x:v>17.8603994846344</x:v>
       </x:c>
       <x:c r="AC20" s="11">
-        <x:v>28.62950086593628</x:v>
+        <x:v>18.178199529647827</x:v>
       </x:c>
       <x:c r="AD20" s="11">
-        <x:v>30.594000816345215</x:v>
+        <x:v>17.910200357437134</x:v>
       </x:c>
       <x:c r="AE20" s="7">
-        <x:v>113.4895</x:v>
+        <x:v>105.2949</x:v>
       </x:c>
       <x:c r="AF20" s="7">
-        <x:v>0.2771119795223347</x:v>
+        <x:v>0.17527202172184977</x:v>
       </x:c>
       <x:c r="AG20" s="7" t="inlineStr">
         <x:is>
-          <x:t>supplement/raw/reports/same_device_20261029_02/same_device_baseline.json</x:t>
+          <x:t>raw/reports/visible_page1g_final_performance.json</x:t>
         </x:is>
       </x:c>
     </x:row>
